--- a/inasistencias-6A-InstrumentalYsitsElectricos/Alumnos-6A-InstrumentalYsistElect.xlsx
+++ b/inasistencias-6A-InstrumentalYsitsElectricos/Alumnos-6A-InstrumentalYsistElect.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="asistencia" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="99">
   <si>
     <t xml:space="preserve">Carpeta</t>
   </si>
@@ -138,6 +138,9 @@
     <t xml:space="preserve">ZARRAGA</t>
   </si>
   <si>
+    <t xml:space="preserve">media</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nombre</t>
   </si>
   <si>
@@ -166,6 +169,12 @@
   </si>
   <si>
     <t xml:space="preserve">val ped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chorico-pineros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nota</t>
   </si>
   <si>
     <t xml:space="preserve">Lucila Yanel</t>
@@ -397,7 +406,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -430,6 +439,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -439,7 +452,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="10">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -535,6 +548,52 @@
         <color rgb="FF000000"/>
         <sz val="12"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF006600"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFCC"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FFCC0000"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC0000"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
   </dxfs>
   <colors>
@@ -711,14 +770,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XDK24"/>
+  <dimension ref="A1:XDL27"/>
   <sheetFormatPr defaultColWidth="9.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="12" min="3" style="1" width="9.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="979" min="979" style="1" width="9.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16337" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="22" min="3" style="1" width="9.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="980" min="980" style="1" width="9.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16338" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -798,88 +857,91 @@
       <c r="X2" s="3" t="n">
         <v>46198</v>
       </c>
-      <c r="Y2" s="3" t="n">
+      <c r="Y2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z2" s="3" t="n">
         <v>46205</v>
       </c>
-      <c r="Z2" s="3" t="n">
+      <c r="AA2" s="3" t="n">
         <v>46212</v>
       </c>
-      <c r="AA2" s="3" t="n">
+      <c r="AB2" s="3" t="n">
         <v>46219</v>
       </c>
-      <c r="AB2" s="3" t="n">
+      <c r="AC2" s="3" t="n">
         <v>46226</v>
       </c>
-      <c r="AC2" s="3" t="n">
+      <c r="AD2" s="3" t="n">
         <v>46233</v>
       </c>
-      <c r="AD2" s="3" t="n">
+      <c r="AE2" s="3" t="n">
         <v>46240</v>
       </c>
-      <c r="AE2" s="3" t="n">
+      <c r="AF2" s="3" t="n">
         <v>46247</v>
       </c>
-      <c r="AF2" s="3" t="n">
+      <c r="AG2" s="3" t="n">
         <v>46254</v>
       </c>
-      <c r="AG2" s="3" t="n">
+      <c r="AH2" s="3" t="n">
         <v>46261</v>
       </c>
-      <c r="AH2" s="3" t="n">
+      <c r="AI2" s="3" t="n">
         <v>46268</v>
       </c>
-      <c r="AI2" s="3" t="n">
+      <c r="AJ2" s="3" t="n">
         <v>46275</v>
       </c>
-      <c r="AJ2" s="3" t="n">
+      <c r="AK2" s="3" t="n">
         <v>46282</v>
       </c>
-      <c r="AK2" s="3" t="n">
+      <c r="AL2" s="3" t="n">
         <v>46289</v>
       </c>
-      <c r="AL2" s="3" t="n">
+      <c r="AM2" s="3" t="n">
         <v>46296</v>
       </c>
-      <c r="AM2" s="3" t="n">
+      <c r="AN2" s="3" t="n">
         <v>46303</v>
       </c>
-      <c r="AN2" s="3" t="n">
+      <c r="AO2" s="3" t="n">
         <v>46310</v>
       </c>
-      <c r="AO2" s="3" t="n">
+      <c r="AP2" s="3" t="n">
         <v>46317</v>
       </c>
-      <c r="AP2" s="3" t="n">
+      <c r="AQ2" s="3" t="n">
         <v>46324</v>
       </c>
-      <c r="AQ2" s="3" t="n">
+      <c r="AR2" s="3" t="n">
         <v>46331</v>
       </c>
-      <c r="AR2" s="3" t="n">
+      <c r="AS2" s="3" t="n">
         <v>46338</v>
       </c>
-      <c r="AS2" s="3" t="n">
+      <c r="AT2" s="3" t="n">
         <v>46345</v>
       </c>
-      <c r="AT2" s="3" t="n">
+      <c r="AU2" s="3" t="n">
         <v>46352</v>
       </c>
-      <c r="AU2" s="3" t="n">
+      <c r="AV2" s="3" t="n">
         <v>46359</v>
       </c>
-      <c r="AV2" s="3" t="n">
+      <c r="AW2" s="3" t="n">
         <v>46366</v>
       </c>
-      <c r="AW2" s="3" t="n">
+      <c r="AX2" s="3" t="n">
         <v>46373</v>
       </c>
-      <c r="AX2" s="3" t="n">
+      <c r="AY2" s="3" t="n">
         <v>46380</v>
       </c>
-      <c r="AY2" s="3" t="n">
+      <c r="AZ2" s="3" t="n">
         <v>46387</v>
       </c>
-      <c r="AZ2" s="3"/>
+      <c r="BA2" s="3"/>
     </row>
     <row r="3" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -951,6 +1013,12 @@
       <c r="W3" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="X3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y3" s="4" t="n">
+        <v>0.791666666666667</v>
+      </c>
     </row>
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
@@ -1019,6 +1087,9 @@
       <c r="W4" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="X4" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -1087,6 +1158,9 @@
       <c r="W5" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="X5" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -1155,6 +1229,9 @@
       <c r="W6" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="X6" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -1223,6 +1300,9 @@
       <c r="W7" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="X7" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="8" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -1291,7 +1371,9 @@
       <c r="W8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="AKQ8" s="1"/>
+      <c r="X8" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="AKR8" s="1"/>
       <c r="AKS8" s="1"/>
       <c r="AKT8" s="1"/>
@@ -1346,9 +1428,10 @@
       <c r="AMQ8" s="1"/>
       <c r="AMR8" s="1"/>
       <c r="AMS8" s="1"/>
-      <c r="XDI8" s="1"/>
+      <c r="AMT8" s="1"/>
       <c r="XDJ8" s="1"/>
       <c r="XDK8" s="1"/>
+      <c r="XDL8" s="1"/>
     </row>
     <row r="9" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
@@ -1417,6 +1500,9 @@
       <c r="W9" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="X9" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
@@ -1485,6 +1571,9 @@
       <c r="W10" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="X10" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -1553,6 +1642,9 @@
       <c r="W11" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="X11" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="12" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="n">
@@ -1627,7 +1719,9 @@
       <c r="W12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="AKQ12" s="6"/>
+      <c r="X12" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="AKR12" s="6"/>
       <c r="AKS12" s="6"/>
       <c r="AKT12" s="6"/>
@@ -1682,9 +1776,10 @@
       <c r="AMQ12" s="6"/>
       <c r="AMR12" s="6"/>
       <c r="AMS12" s="6"/>
-      <c r="XDI12" s="6"/>
+      <c r="AMT12" s="6"/>
       <c r="XDJ12" s="6"/>
       <c r="XDK12" s="6"/>
+      <c r="XDL12" s="6"/>
     </row>
     <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
@@ -1754,6 +1849,9 @@
       <c r="W13" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="X13" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -1823,6 +1921,9 @@
       <c r="W14" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="X14" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="15" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="n">
@@ -1894,7 +1995,9 @@
       <c r="W15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="AKQ15" s="6"/>
+      <c r="X15" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="AKR15" s="6"/>
       <c r="AKS15" s="6"/>
       <c r="AKT15" s="6"/>
@@ -1949,9 +2052,10 @@
       <c r="AMQ15" s="6"/>
       <c r="AMR15" s="6"/>
       <c r="AMS15" s="6"/>
-      <c r="XDI15" s="6"/>
+      <c r="AMT15" s="6"/>
       <c r="XDJ15" s="6"/>
       <c r="XDK15" s="6"/>
+      <c r="XDL15" s="6"/>
     </row>
     <row r="16" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
@@ -2021,6 +2125,9 @@
       <c r="W16" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="X16" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="17" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
@@ -2090,6 +2197,9 @@
       <c r="W17" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="X17" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="18" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="n">
@@ -2161,7 +2271,9 @@
       <c r="W18" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="AKQ18" s="6"/>
+      <c r="X18" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="AKR18" s="6"/>
       <c r="AKS18" s="6"/>
       <c r="AKT18" s="6"/>
@@ -2216,9 +2328,10 @@
       <c r="AMQ18" s="6"/>
       <c r="AMR18" s="6"/>
       <c r="AMS18" s="6"/>
-      <c r="XDI18" s="6"/>
+      <c r="AMT18" s="6"/>
       <c r="XDJ18" s="6"/>
       <c r="XDK18" s="6"/>
+      <c r="XDL18" s="6"/>
     </row>
     <row r="19" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="n">
@@ -2290,7 +2403,9 @@
       <c r="W19" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="AKQ19" s="6"/>
+      <c r="X19" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="AKR19" s="6"/>
       <c r="AKS19" s="6"/>
       <c r="AKT19" s="6"/>
@@ -2345,9 +2460,10 @@
       <c r="AMQ19" s="6"/>
       <c r="AMR19" s="6"/>
       <c r="AMS19" s="6"/>
-      <c r="XDI19" s="6"/>
+      <c r="AMT19" s="6"/>
       <c r="XDJ19" s="6"/>
       <c r="XDK19" s="6"/>
+      <c r="XDL19" s="6"/>
     </row>
     <row r="20" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
@@ -2417,6 +2533,9 @@
       <c r="W20" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="X20" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="21" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
@@ -2488,6 +2607,12 @@
       </c>
       <c r="W21" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y21" s="4" t="n">
+        <v>0.791666666666667</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2559,7 +2684,9 @@
       <c r="W22" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="X22" s="1"/>
+      <c r="X22" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
       <c r="AA22" s="1"/>
@@ -3569,9 +3696,10 @@
       <c r="AMQ22" s="1"/>
       <c r="AMR22" s="1"/>
       <c r="AMS22" s="1"/>
-      <c r="XDI22" s="1"/>
+      <c r="AMT22" s="1"/>
       <c r="XDJ22" s="1"/>
       <c r="XDK22" s="1"/>
+      <c r="XDL22" s="1"/>
     </row>
     <row r="23" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="n">
@@ -3645,7 +3773,9 @@
       <c r="W23" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="X23" s="7"/>
+      <c r="X23" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="Y23" s="7"/>
       <c r="Z23" s="7"/>
       <c r="AA23" s="7"/>
@@ -4600,6 +4730,7 @@
       <c r="AKN23" s="7"/>
       <c r="AKO23" s="7"/>
       <c r="AKP23" s="7"/>
+      <c r="AKQ23" s="7"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="1" t="s">
@@ -4641,13 +4772,6 @@
         <f aca="false">COUNTIF(M3:M23,"P")</f>
         <v>12</v>
       </c>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
       <c r="U24" s="1" t="n">
         <f aca="false">COUNTIF(U3:U23,"P")</f>
         <v>13</v>
@@ -4659,6 +4783,49 @@
       <c r="W24" s="1" t="n">
         <f aca="false">COUNTIF(W3:W23,"P")</f>
         <v>14</v>
+      </c>
+      <c r="X24" s="1" t="n">
+        <f aca="false">COUNTIF(X3:X23,"P")</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W25" s="1" t="n">
+        <f aca="false">COUNTIF(W3:W23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="X25" s="1" t="n">
+        <f aca="false">COUNTIF(X3:X23,"M")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="W26" s="1" t="n">
+        <f aca="false">COUNTIF(W3:W23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="X26" s="1" t="n">
+        <f aca="false">COUNTIF(X3:X23,"T")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="W27" s="1" t="n">
+        <f aca="false">SUM(W24:W26)</f>
+        <v>14</v>
+      </c>
+      <c r="X27" s="1" t="n">
+        <f aca="false">SUM(X24:X26)</f>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -4705,9 +4872,12 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.34"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="35.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10.37"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="1" width="8.68"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="6" min="6" style="1" width="11.78"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="9" min="7" style="0" width="8.75"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="10" style="1" width="10.37"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="11" min="11" style="0" width="8.75"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="13" min="13" style="0" width="8.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16145" style="1" width="10.58"/>
   </cols>
   <sheetData>
@@ -4722,40 +4892,46 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4763,13 +4939,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>8</v>
@@ -4797,19 +4973,30 @@
         <f aca="false">IF(L3&gt;6,"TEA",IF(L3&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N3" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="O3" s="0" t="n">
+        <f aca="false">IF(AND(L3&gt;6,N3&gt;6),ROUND((L3+N3)/2,0),MIN(L3,N3))</f>
+        <v>8</v>
+      </c>
+      <c r="P3" s="5" t="str">
+        <f aca="false">IF(O3&gt;6,"TEA",IF(O3&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>10</v>
@@ -4837,19 +5024,30 @@
         <f aca="false">IF(L4&gt;6,"TEA",IF(L4&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N4" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="O4" s="0" t="n">
+        <f aca="false">IF(AND(L4&gt;6,N4&gt;6),ROUND((L4+N4)/2,0),MIN(L4,N4))</f>
+        <v>8</v>
+      </c>
+      <c r="P4" s="5" t="str">
+        <f aca="false">IF(O4&gt;6,"TEA",IF(O4&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>1</v>
@@ -4877,19 +5075,30 @@
         <f aca="false">IF(L5&gt;6,"TEA",IF(L5&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
+      <c r="N5" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="O5" s="0" t="n">
+        <f aca="false">IF(AND(L5&gt;6,N5&gt;6),ROUND((L5+N5)/2,0),MIN(L5,N5))</f>
+        <v>6</v>
+      </c>
+      <c r="P5" s="5" t="str">
+        <f aca="false">IF(O5&gt;6,"TEA",IF(O5&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>10</v>
@@ -4917,19 +5126,30 @@
         <f aca="false">IF(L6&gt;6,"TEA",IF(L6&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N6" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="O6" s="0" t="n">
+        <f aca="false">IF(AND(L6&gt;6,N6&gt;6),ROUND((L6+N6)/2,0),MIN(L6,N6))</f>
+        <v>9</v>
+      </c>
+      <c r="P6" s="5" t="str">
+        <f aca="false">IF(O6&gt;6,"TEA",IF(O6&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>8</v>
@@ -4960,19 +5180,30 @@
         <f aca="false">IF(L7&gt;6,"TEA",IF(L7&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N7" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="O7" s="0" t="n">
+        <f aca="false">IF(AND(L7&gt;6,N7&gt;6),ROUND((L7+N7)/2,0),MIN(L7,N7))</f>
+        <v>9</v>
+      </c>
+      <c r="P7" s="5" t="str">
+        <f aca="false">IF(O7&gt;6,"TEA",IF(O7&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="8" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>8</v>
@@ -5001,9 +5232,17 @@
         <f aca="false">IF(L8&gt;6,"TEA",IF(L8&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
+      <c r="N8" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="O8" s="0" t="n">
+        <f aca="false">IF(AND(L8&gt;6,N8&gt;6),ROUND((L8+N8)/2,0),MIN(L8,N8))</f>
+        <v>9</v>
+      </c>
+      <c r="P8" s="5" t="str">
+        <f aca="false">IF(O8&gt;6,"TEA",IF(O8&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
@@ -5158,13 +5397,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>8</v>
@@ -5192,19 +5431,30 @@
         <f aca="false">IF(L9&gt;6,"TEA",IF(L9&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="O9" s="0" t="n">
+        <f aca="false">IF(AND(L9&gt;6,N9&gt;6),ROUND((L9+N9)/2,0),MIN(L9,N9))</f>
+        <v>8</v>
+      </c>
+      <c r="P9" s="5" t="str">
+        <f aca="false">IF(O9&gt;6,"TEA",IF(O9&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>10</v>
@@ -5232,19 +5482,30 @@
         <f aca="false">IF(L10&gt;6,"TEA",IF(L10&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N10" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="O10" s="0" t="n">
+        <f aca="false">IF(AND(L10&gt;6,N10&gt;6),ROUND((L10+N10)/2,0),MIN(L10,N10))</f>
+        <v>9</v>
+      </c>
+      <c r="P10" s="5" t="str">
+        <f aca="false">IF(O10&gt;6,"TEA",IF(O10&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>10</v>
@@ -5272,19 +5533,30 @@
         <f aca="false">IF(L11&gt;6,"TEA",IF(L11&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N11" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="O11" s="0" t="n">
+        <f aca="false">IF(AND(L11&gt;6,N11&gt;6),ROUND((L11+N11)/2,0),MIN(L11,N11))</f>
+        <v>9</v>
+      </c>
+      <c r="P11" s="5" t="str">
+        <f aca="false">IF(O11&gt;6,"TEA",IF(O11&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="12" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
@@ -5313,9 +5585,17 @@
         <f aca="false">IF(L12&gt;6,"TEA",IF(L12&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
+      <c r="N12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="0" t="n">
+        <f aca="false">IF(AND(L12&gt;6,N12&gt;6),ROUND((L12+N12)/2,0),MIN(L12,N12))</f>
+        <v>1</v>
+      </c>
+      <c r="P12" s="5" t="str">
+        <f aca="false">IF(O12&gt;6,"TEA",IF(O12&gt;3,"TEP","TED"))</f>
+        <v>TED</v>
+      </c>
       <c r="Q12" s="6"/>
       <c r="R12" s="6"/>
       <c r="S12" s="6"/>
@@ -5470,13 +5750,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>10</v>
@@ -5505,19 +5785,30 @@
         <f aca="false">IF(L13&gt;6,"TEA",IF(L13&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N13" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="O13" s="0" t="n">
+        <f aca="false">IF(AND(L13&gt;6,N13&gt;6),ROUND((L13+N13)/2,0),MIN(L13,N13))</f>
+        <v>9</v>
+      </c>
+      <c r="P13" s="5" t="str">
+        <f aca="false">IF(O13&gt;6,"TEA",IF(O13&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>10</v>
@@ -5546,19 +5837,30 @@
         <f aca="false">IF(L14&gt;6,"TEA",IF(L14&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N14" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="O14" s="0" t="n">
+        <f aca="false">IF(AND(L14&gt;6,N14&gt;6),ROUND((L14+N14)/2,0),MIN(L14,N14))</f>
+        <v>9</v>
+      </c>
+      <c r="P14" s="5" t="str">
+        <f aca="false">IF(O14&gt;6,"TEA",IF(O14&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="15" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="n">
         <v>13</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>1</v>
@@ -5587,9 +5889,17 @@
         <f aca="false">IF(L15&gt;6,"TEA",IF(L15&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
+      <c r="N15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="0" t="n">
+        <f aca="false">IF(AND(L15&gt;6,N15&gt;6),ROUND((L15+N15)/2,0),MIN(L15,N15))</f>
+        <v>1</v>
+      </c>
+      <c r="P15" s="5" t="str">
+        <f aca="false">IF(O15&gt;6,"TEA",IF(O15&gt;3,"TEP","TED"))</f>
+        <v>TED</v>
+      </c>
       <c r="Q15" s="6"/>
       <c r="R15" s="6"/>
       <c r="S15" s="6"/>
@@ -5744,13 +6054,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>8</v>
@@ -5779,19 +6089,30 @@
         <f aca="false">IF(L16&gt;6,"TEA",IF(L16&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N16" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="O16" s="0" t="n">
+        <f aca="false">IF(AND(L16&gt;6,N16&gt;6),ROUND((L16+N16)/2,0),MIN(L16,N16))</f>
+        <v>9</v>
+      </c>
+      <c r="P16" s="5" t="str">
+        <f aca="false">IF(O16&gt;6,"TEA",IF(O16&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="17" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>10</v>
@@ -5820,19 +6141,30 @@
         <f aca="false">IF(L17&gt;6,"TEA",IF(L17&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N17" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="O17" s="0" t="n">
+        <f aca="false">IF(AND(L17&gt;6,N17&gt;6),ROUND((L17+N17)/2,0),MIN(L17,N17))</f>
+        <v>8</v>
+      </c>
+      <c r="P17" s="5" t="str">
+        <f aca="false">IF(O17&gt;6,"TEA",IF(O17&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="18" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="n">
         <v>16</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>1</v>
@@ -5861,9 +6193,17 @@
         <f aca="false">IF(L18&gt;6,"TEA",IF(L18&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
+      <c r="N18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="0" t="n">
+        <f aca="false">IF(AND(L18&gt;6,N18&gt;6),ROUND((L18+N18)/2,0),MIN(L18,N18))</f>
+        <v>1</v>
+      </c>
+      <c r="P18" s="5" t="str">
+        <f aca="false">IF(O18&gt;6,"TEA",IF(O18&gt;3,"TEP","TED"))</f>
+        <v>TED</v>
+      </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
       <c r="S18" s="6"/>
@@ -6018,13 +6358,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>1</v>
@@ -6053,9 +6393,17 @@
         <f aca="false">IF(L19&gt;6,"TEA",IF(L19&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
+      <c r="N19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="0" t="n">
+        <f aca="false">IF(AND(L19&gt;6,N19&gt;6),ROUND((L19+N19)/2,0),MIN(L19,N19))</f>
+        <v>1</v>
+      </c>
+      <c r="P19" s="5" t="str">
+        <f aca="false">IF(O19&gt;6,"TEA",IF(O19&gt;3,"TEP","TED"))</f>
+        <v>TED</v>
+      </c>
       <c r="Q19" s="6"/>
       <c r="R19" s="6"/>
       <c r="S19" s="6"/>
@@ -6210,13 +6558,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>10</v>
@@ -6245,19 +6593,30 @@
         <f aca="false">IF(L20&gt;6,"TEA",IF(L20&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
+      <c r="N20" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="O20" s="0" t="n">
+        <f aca="false">IF(AND(L20&gt;6,N20&gt;6),ROUND((L20+N20)/2,0),MIN(L20,N20))</f>
+        <v>5</v>
+      </c>
+      <c r="P20" s="5" t="str">
+        <f aca="false">IF(O20&gt;6,"TEA",IF(O20&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
+      </c>
     </row>
     <row r="21" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>7</v>
@@ -6286,19 +6645,30 @@
         <f aca="false">IF(L21&gt;6,"TEA",IF(L21&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N21" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="O21" s="0" t="n">
+        <f aca="false">IF(AND(L21&gt;6,N21&gt;6),ROUND((L21+N21)/2,0),MIN(L21,N21))</f>
+        <v>8</v>
+      </c>
+      <c r="P21" s="5" t="str">
+        <f aca="false">IF(O21&gt;6,"TEA",IF(O21&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="22" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>10</v>
@@ -6325,6 +6695,17 @@
       </c>
       <c r="M22" s="5" t="str">
         <f aca="false">IF(L22&gt;6,"TEA",IF(L22&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="N22" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="O22" s="0" t="n">
+        <f aca="false">IF(AND(L22&gt;6,N22&gt;6),ROUND((L22+N22)/2,0),MIN(L22,N22))</f>
+        <v>9</v>
+      </c>
+      <c r="P22" s="5" t="str">
+        <f aca="false">IF(O22&gt;6,"TEA",IF(O22&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
       <c r="WYA22" s="2"/>
@@ -6519,13 +6900,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>36</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>1</v>
@@ -6554,9 +6935,17 @@
         <f aca="false">IF(L23&gt;6,"TEA",IF(L23&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
+      <c r="N23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="0" t="n">
+        <f aca="false">IF(AND(L23&gt;6,N23&gt;6),ROUND((L23+N23)/2,0),MIN(L23,N23))</f>
+        <v>1</v>
+      </c>
+      <c r="P23" s="5" t="str">
+        <f aca="false">IF(O23&gt;6,"TEA",IF(O23&gt;3,"TEP","TED"))</f>
+        <v>TED</v>
+      </c>
       <c r="Q23" s="6"/>
       <c r="R23" s="6"/>
       <c r="S23" s="6"/>
@@ -6893,7 +7282,7 @@
       <c r="XFD23" s="6"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E3:M23">
+  <conditionalFormatting sqref="E3:M23 P3:P23">
     <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
@@ -6915,6 +7304,18 @@
     </cfRule>
     <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>"TED"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N3:O23">
+    <cfRule type="cellIs" priority="9" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>6</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>4</formula>
+      <formula>6</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6952,16 +7353,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7380,7 +7781,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F29" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G29" s="1" t="n">
         <f aca="false">COUNTIF(G2:G28,"&gt;0")</f>
@@ -7422,7 +7823,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7747,16 +8148,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8211,7 +8612,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/inasistencias-6A-InstrumentalYsitsElectricos/Alumnos-6A-InstrumentalYsistElect.xlsx
+++ b/inasistencias-6A-InstrumentalYsitsElectricos/Alumnos-6A-InstrumentalYsistElect.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="asistencia" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="99">
   <si>
     <t xml:space="preserve">Carpeta</t>
   </si>
@@ -406,7 +406,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -436,10 +436,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -562,7 +558,6 @@
           <bgColor rgb="FFCCFFCC"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -577,7 +572,6 @@
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -593,7 +587,6 @@
           <bgColor rgb="FFCC0000"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
   </dxfs>
   <colors>
@@ -861,7 +854,7 @@
         <v>3</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>46205</v>
+        <v>46254</v>
       </c>
       <c r="AA2" s="3" t="n">
         <v>46212</v>
@@ -1019,6 +1012,9 @@
       <c r="Y3" s="4" t="n">
         <v>0.791666666666667</v>
       </c>
+      <c r="Z3" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
@@ -1090,6 +1086,9 @@
       <c r="X4" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="Z4" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -1161,6 +1160,9 @@
       <c r="X5" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="Z5" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -1232,6 +1234,9 @@
       <c r="X6" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="Z6" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -1303,6 +1308,9 @@
       <c r="X7" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="Z7" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="8" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -1373,6 +1381,9 @@
       </c>
       <c r="X8" s="2" t="s">
         <v>11</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="AKR8" s="1"/>
       <c r="AKS8" s="1"/>
@@ -1503,6 +1514,9 @@
       <c r="X9" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="Z9" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
@@ -1574,6 +1588,9 @@
       <c r="X10" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="Z10" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -1645,6 +1662,9 @@
       <c r="X11" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="Z11" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="12" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="n">
@@ -1720,6 +1740,9 @@
         <v>12</v>
       </c>
       <c r="X12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="AKR12" s="6"/>
@@ -1852,6 +1875,9 @@
       <c r="X13" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="Z13" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -1924,6 +1950,9 @@
       <c r="X14" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="Z14" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="15" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="n">
@@ -1996,6 +2025,9 @@
         <v>12</v>
       </c>
       <c r="X15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z15" s="1" t="s">
         <v>12</v>
       </c>
       <c r="AKR15" s="6"/>
@@ -2128,6 +2160,9 @@
       <c r="X16" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="Z16" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="17" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
@@ -2200,6 +2235,9 @@
       <c r="X17" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="Z17" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="18" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="n">
@@ -2272,6 +2310,9 @@
         <v>12</v>
       </c>
       <c r="X18" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="AKR18" s="6"/>
@@ -2406,6 +2447,9 @@
       <c r="X19" s="7" t="s">
         <v>12</v>
       </c>
+      <c r="Z19" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="AKR19" s="6"/>
       <c r="AKS19" s="6"/>
       <c r="AKT19" s="6"/>
@@ -2536,6 +2580,9 @@
       <c r="X20" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="Z20" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="21" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
@@ -2613,6 +2660,9 @@
       </c>
       <c r="Y21" s="4" t="n">
         <v>0.791666666666667</v>
+      </c>
+      <c r="Z21" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2688,7 +2738,9 @@
         <v>11</v>
       </c>
       <c r="Y22" s="1"/>
-      <c r="Z22" s="1"/>
+      <c r="Z22" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
@@ -3777,7 +3829,9 @@
         <v>12</v>
       </c>
       <c r="Y23" s="7"/>
-      <c r="Z23" s="7"/>
+      <c r="Z23" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="AA23" s="7"/>
       <c r="AB23" s="7"/>
       <c r="AC23" s="7"/>
@@ -4788,6 +4842,10 @@
         <f aca="false">COUNTIF(X3:X23,"P")</f>
         <v>13</v>
       </c>
+      <c r="Z24" s="1" t="n">
+        <f aca="false">COUNTIF(Z3:Z23,"P")</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="1" t="s">
@@ -4801,6 +4859,10 @@
         <f aca="false">COUNTIF(X3:X23,"M")</f>
         <v>0</v>
       </c>
+      <c r="Z25" s="1" t="n">
+        <f aca="false">COUNTIF(Z3:Z23,"M")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="1" t="s">
@@ -4814,6 +4876,10 @@
         <f aca="false">COUNTIF(X3:X23,"T")</f>
         <v>2</v>
       </c>
+      <c r="Z26" s="1" t="n">
+        <f aca="false">COUNTIF(Z3:Z23,"T")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="s">
@@ -4826,6 +4892,10 @@
       <c r="X27" s="1" t="n">
         <f aca="false">SUM(X24:X26)</f>
         <v>15</v>
+      </c>
+      <c r="Z27" s="1" t="n">
+        <f aca="false">SUM(Z24:Z26)</f>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4874,10 +4944,10 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="35.71"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="1" width="8.68"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="6" min="6" style="1" width="11.78"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="9" min="7" style="0" width="8.75"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="9" min="7" style="1" width="8.75"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="10" style="1" width="10.37"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="11" min="11" style="0" width="8.75"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="13" min="13" style="0" width="8.75"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="11" min="11" style="1" width="8.75"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="13" min="13" style="1" width="8.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16145" style="1" width="10.58"/>
   </cols>
   <sheetData>
@@ -4927,10 +4997,10 @@
       <c r="M2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="O2" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -4956,6 +5026,7 @@
       <c r="G3" s="5" t="n">
         <v>5</v>
       </c>
+      <c r="H3" s="5"/>
       <c r="I3" s="5" t="n">
         <v>5</v>
       </c>
@@ -4973,10 +5044,10 @@
         <f aca="false">IF(L3&gt;6,"TEA",IF(L3&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N3" s="0" t="n">
+      <c r="N3" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O3" s="0" t="n">
+      <c r="O3" s="1" t="n">
         <f aca="false">IF(AND(L3&gt;6,N3&gt;6),ROUND((L3+N3)/2,0),MIN(L3,N3))</f>
         <v>8</v>
       </c>
@@ -5007,6 +5078,7 @@
       <c r="G4" s="5" t="n">
         <v>8</v>
       </c>
+      <c r="H4" s="5"/>
       <c r="I4" s="5" t="n">
         <v>7</v>
       </c>
@@ -5024,10 +5096,10 @@
         <f aca="false">IF(L4&gt;6,"TEA",IF(L4&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O4" s="0" t="n">
+      <c r="O4" s="1" t="n">
         <f aca="false">IF(AND(L4&gt;6,N4&gt;6),ROUND((L4+N4)/2,0),MIN(L4,N4))</f>
         <v>8</v>
       </c>
@@ -5058,6 +5130,7 @@
       <c r="G5" s="5" t="n">
         <v>7</v>
       </c>
+      <c r="H5" s="5"/>
       <c r="I5" s="5" t="n">
         <v>7</v>
       </c>
@@ -5075,10 +5148,10 @@
         <f aca="false">IF(L5&gt;6,"TEA",IF(L5&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O5" s="0" t="n">
+      <c r="O5" s="1" t="n">
         <f aca="false">IF(AND(L5&gt;6,N5&gt;6),ROUND((L5+N5)/2,0),MIN(L5,N5))</f>
         <v>6</v>
       </c>
@@ -5109,6 +5182,7 @@
       <c r="G6" s="5" t="n">
         <v>10</v>
       </c>
+      <c r="H6" s="5"/>
       <c r="I6" s="5" t="n">
         <v>10</v>
       </c>
@@ -5126,10 +5200,10 @@
         <f aca="false">IF(L6&gt;6,"TEA",IF(L6&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O6" s="0" t="n">
+      <c r="O6" s="1" t="n">
         <f aca="false">IF(AND(L6&gt;6,N6&gt;6),ROUND((L6+N6)/2,0),MIN(L6,N6))</f>
         <v>9</v>
       </c>
@@ -5180,10 +5254,10 @@
         <f aca="false">IF(L7&gt;6,"TEA",IF(L7&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O7" s="0" t="n">
+      <c r="O7" s="1" t="n">
         <f aca="false">IF(AND(L7&gt;6,N7&gt;6),ROUND((L7+N7)/2,0),MIN(L7,N7))</f>
         <v>9</v>
       </c>
@@ -5232,10 +5306,10 @@
         <f aca="false">IF(L8&gt;6,"TEA",IF(L8&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N8" s="0" t="n">
+      <c r="N8" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O8" s="0" t="n">
+      <c r="O8" s="1" t="n">
         <f aca="false">IF(AND(L8&gt;6,N8&gt;6),ROUND((L8+N8)/2,0),MIN(L8,N8))</f>
         <v>9</v>
       </c>
@@ -5414,6 +5488,7 @@
       <c r="G9" s="5" t="n">
         <v>8</v>
       </c>
+      <c r="H9" s="5"/>
       <c r="I9" s="5" t="n">
         <v>1</v>
       </c>
@@ -5431,10 +5506,10 @@
         <f aca="false">IF(L9&gt;6,"TEA",IF(L9&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N9" s="0" t="n">
+      <c r="N9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O9" s="0" t="n">
+      <c r="O9" s="1" t="n">
         <f aca="false">IF(AND(L9&gt;6,N9&gt;6),ROUND((L9+N9)/2,0),MIN(L9,N9))</f>
         <v>8</v>
       </c>
@@ -5465,6 +5540,7 @@
       <c r="G10" s="5" t="n">
         <v>10</v>
       </c>
+      <c r="H10" s="5"/>
       <c r="I10" s="5" t="n">
         <v>10</v>
       </c>
@@ -5482,10 +5558,10 @@
         <f aca="false">IF(L10&gt;6,"TEA",IF(L10&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N10" s="0" t="n">
+      <c r="N10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O10" s="0" t="n">
+      <c r="O10" s="1" t="n">
         <f aca="false">IF(AND(L10&gt;6,N10&gt;6),ROUND((L10+N10)/2,0),MIN(L10,N10))</f>
         <v>9</v>
       </c>
@@ -5516,6 +5592,7 @@
       <c r="G11" s="5" t="n">
         <v>10</v>
       </c>
+      <c r="H11" s="5"/>
       <c r="I11" s="5" t="n">
         <v>6</v>
       </c>
@@ -5533,10 +5610,10 @@
         <f aca="false">IF(L11&gt;6,"TEA",IF(L11&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N11" s="0" t="n">
+      <c r="N11" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O11" s="0" t="n">
+      <c r="O11" s="1" t="n">
         <f aca="false">IF(AND(L11&gt;6,N11&gt;6),ROUND((L11+N11)/2,0),MIN(L11,N11))</f>
         <v>9</v>
       </c>
@@ -5585,10 +5662,10 @@
         <f aca="false">IF(L12&gt;6,"TEA",IF(L12&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="N12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" s="0" t="n">
+      <c r="N12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1" t="n">
         <f aca="false">IF(AND(L12&gt;6,N12&gt;6),ROUND((L12+N12)/2,0),MIN(L12,N12))</f>
         <v>1</v>
       </c>
@@ -5785,10 +5862,10 @@
         <f aca="false">IF(L13&gt;6,"TEA",IF(L13&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N13" s="0" t="n">
+      <c r="N13" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O13" s="0" t="n">
+      <c r="O13" s="1" t="n">
         <f aca="false">IF(AND(L13&gt;6,N13&gt;6),ROUND((L13+N13)/2,0),MIN(L13,N13))</f>
         <v>9</v>
       </c>
@@ -5837,10 +5914,10 @@
         <f aca="false">IF(L14&gt;6,"TEA",IF(L14&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N14" s="0" t="n">
+      <c r="N14" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O14" s="0" t="n">
+      <c r="O14" s="1" t="n">
         <f aca="false">IF(AND(L14&gt;6,N14&gt;6),ROUND((L14+N14)/2,0),MIN(L14,N14))</f>
         <v>9</v>
       </c>
@@ -5889,10 +5966,10 @@
         <f aca="false">IF(L15&gt;6,"TEA",IF(L15&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="N15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" s="0" t="n">
+      <c r="N15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="1" t="n">
         <f aca="false">IF(AND(L15&gt;6,N15&gt;6),ROUND((L15+N15)/2,0),MIN(L15,N15))</f>
         <v>1</v>
       </c>
@@ -6089,10 +6166,10 @@
         <f aca="false">IF(L16&gt;6,"TEA",IF(L16&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N16" s="0" t="n">
+      <c r="N16" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O16" s="0" t="n">
+      <c r="O16" s="1" t="n">
         <f aca="false">IF(AND(L16&gt;6,N16&gt;6),ROUND((L16+N16)/2,0),MIN(L16,N16))</f>
         <v>9</v>
       </c>
@@ -6141,10 +6218,10 @@
         <f aca="false">IF(L17&gt;6,"TEA",IF(L17&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N17" s="0" t="n">
+      <c r="N17" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O17" s="0" t="n">
+      <c r="O17" s="1" t="n">
         <f aca="false">IF(AND(L17&gt;6,N17&gt;6),ROUND((L17+N17)/2,0),MIN(L17,N17))</f>
         <v>8</v>
       </c>
@@ -6193,10 +6270,10 @@
         <f aca="false">IF(L18&gt;6,"TEA",IF(L18&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="N18" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" s="0" t="n">
+      <c r="N18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="1" t="n">
         <f aca="false">IF(AND(L18&gt;6,N18&gt;6),ROUND((L18+N18)/2,0),MIN(L18,N18))</f>
         <v>1</v>
       </c>
@@ -6393,10 +6470,10 @@
         <f aca="false">IF(L19&gt;6,"TEA",IF(L19&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="N19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" s="0" t="n">
+      <c r="N19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="1" t="n">
         <f aca="false">IF(AND(L19&gt;6,N19&gt;6),ROUND((L19+N19)/2,0),MIN(L19,N19))</f>
         <v>1</v>
       </c>
@@ -6593,10 +6670,10 @@
         <f aca="false">IF(L20&gt;6,"TEA",IF(L20&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
-      <c r="N20" s="0" t="n">
+      <c r="N20" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O20" s="0" t="n">
+      <c r="O20" s="1" t="n">
         <f aca="false">IF(AND(L20&gt;6,N20&gt;6),ROUND((L20+N20)/2,0),MIN(L20,N20))</f>
         <v>5</v>
       </c>
@@ -6645,10 +6722,10 @@
         <f aca="false">IF(L21&gt;6,"TEA",IF(L21&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N21" s="0" t="n">
+      <c r="N21" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O21" s="0" t="n">
+      <c r="O21" s="1" t="n">
         <f aca="false">IF(AND(L21&gt;6,N21&gt;6),ROUND((L21+N21)/2,0),MIN(L21,N21))</f>
         <v>8</v>
       </c>
@@ -6697,10 +6774,10 @@
         <f aca="false">IF(L22&gt;6,"TEA",IF(L22&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N22" s="0" t="n">
+      <c r="N22" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O22" s="0" t="n">
+      <c r="O22" s="1" t="n">
         <f aca="false">IF(AND(L22&gt;6,N22&gt;6),ROUND((L22+N22)/2,0),MIN(L22,N22))</f>
         <v>9</v>
       </c>
@@ -6935,10 +7012,10 @@
         <f aca="false">IF(L23&gt;6,"TEA",IF(L23&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="N23" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" s="0" t="n">
+      <c r="N23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="1" t="n">
         <f aca="false">IF(AND(L23&gt;6,N23&gt;6),ROUND((L23+N23)/2,0),MIN(L23,N23))</f>
         <v>1</v>
       </c>

--- a/inasistencias-6A-InstrumentalYsitsElectricos/Alumnos-6A-InstrumentalYsistElect.xlsx
+++ b/inasistencias-6A-InstrumentalYsitsElectricos/Alumnos-6A-InstrumentalYsistElect.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="103">
   <si>
     <t xml:space="preserve">Carpeta</t>
   </si>
@@ -177,6 +177,15 @@
     <t xml:space="preserve">Nota</t>
   </si>
   <si>
+    <t xml:space="preserve">4-bco de prueba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-Especif DCU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vercel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lucila Yanel</t>
   </si>
   <si>
@@ -265,6 +274,9 @@
   </si>
   <si>
     <t xml:space="preserve">electroariel_@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">modicar en alumnos</t>
   </si>
   <si>
     <t xml:space="preserve">Gabriel Lautaro</t>
@@ -857,19 +869,19 @@
         <v>46254</v>
       </c>
       <c r="AA2" s="3" t="n">
-        <v>46212</v>
+        <v>46268</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>46219</v>
+        <v>46275</v>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>46226</v>
+        <v>46282</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>46233</v>
+        <v>46289</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>46240</v>
+        <v>46296</v>
       </c>
       <c r="AF2" s="3" t="n">
         <v>46247</v>
@@ -1015,6 +1027,21 @@
       <c r="Z3" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AA3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
@@ -1089,6 +1116,21 @@
       <c r="Z4" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AA4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -1163,6 +1205,21 @@
       <c r="Z5" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AA5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE5" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -1237,6 +1294,21 @@
       <c r="Z6" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AA6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE6" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -1311,6 +1383,21 @@
       <c r="Z7" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AA7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE7" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="8" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -1384,6 +1471,21 @@
       </c>
       <c r="Z8" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="AA8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE8" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="AKR8" s="1"/>
       <c r="AKS8" s="1"/>
@@ -1517,6 +1619,21 @@
       <c r="Z9" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AA9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE9" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
@@ -1591,6 +1708,21 @@
       <c r="Z10" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AA10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE10" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -1665,6 +1797,21 @@
       <c r="Z11" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AA11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE11" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="12" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="n">
@@ -1743,6 +1890,21 @@
         <v>12</v>
       </c>
       <c r="Z12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE12" s="7" t="s">
         <v>12</v>
       </c>
       <c r="AKR12" s="6"/>
@@ -1878,6 +2040,21 @@
       <c r="Z13" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AA13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE13" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -1953,6 +2130,21 @@
       <c r="Z14" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AA14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE14" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="15" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="n">
@@ -2028,6 +2220,21 @@
         <v>12</v>
       </c>
       <c r="Z15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE15" s="7" t="s">
         <v>12</v>
       </c>
       <c r="AKR15" s="6"/>
@@ -2163,6 +2370,21 @@
       <c r="Z16" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AA16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE16" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="17" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
@@ -2238,6 +2460,21 @@
       <c r="Z17" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AA17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE17" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="18" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="n">
@@ -2313,6 +2550,21 @@
         <v>12</v>
       </c>
       <c r="Z18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA18" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB18" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC18" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD18" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE18" s="7" t="s">
         <v>12</v>
       </c>
       <c r="AKR18" s="6"/>
@@ -2450,6 +2702,21 @@
       <c r="Z19" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AA19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE19" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="AKR19" s="6"/>
       <c r="AKS19" s="6"/>
       <c r="AKT19" s="6"/>
@@ -2583,6 +2850,21 @@
       <c r="Z20" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="AA20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE20" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="21" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
@@ -2663,6 +2945,21 @@
       </c>
       <c r="Z21" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="AA21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE21" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2741,11 +3038,21 @@
       <c r="Z22" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="AA22" s="1"/>
-      <c r="AB22" s="1"/>
-      <c r="AC22" s="1"/>
-      <c r="AD22" s="1"/>
-      <c r="AE22" s="1"/>
+      <c r="AA22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE22" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="AF22" s="1"/>
       <c r="AG22" s="1"/>
       <c r="AH22" s="1"/>
@@ -3832,11 +4139,21 @@
       <c r="Z23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AA23" s="7"/>
-      <c r="AB23" s="7"/>
-      <c r="AC23" s="7"/>
-      <c r="AD23" s="7"/>
-      <c r="AE23" s="7"/>
+      <c r="AA23" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB23" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC23" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD23" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE23" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="AF23" s="7"/>
       <c r="AG23" s="7"/>
       <c r="AH23" s="7"/>
@@ -4846,6 +5163,26 @@
         <f aca="false">COUNTIF(Z3:Z23,"P")</f>
         <v>2</v>
       </c>
+      <c r="AA24" s="1" t="n">
+        <f aca="false">COUNTIF(AA3:AA23,"P")</f>
+        <v>14</v>
+      </c>
+      <c r="AB24" s="1" t="n">
+        <f aca="false">COUNTIF(AB3:AB23,"P")</f>
+        <v>15</v>
+      </c>
+      <c r="AC24" s="1" t="n">
+        <f aca="false">COUNTIF(AC3:AC23,"P")</f>
+        <v>16</v>
+      </c>
+      <c r="AD24" s="1" t="n">
+        <f aca="false">COUNTIF(AD3:AD23,"P")</f>
+        <v>14</v>
+      </c>
+      <c r="AE24" s="1" t="n">
+        <f aca="false">COUNTIF(AE3:AE23,"P")</f>
+        <v>15</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="1" t="s">
@@ -4863,6 +5200,26 @@
         <f aca="false">COUNTIF(Z3:Z23,"M")</f>
         <v>0</v>
       </c>
+      <c r="AA25" s="1" t="n">
+        <f aca="false">COUNTIF(AA3:AA23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AB25" s="1" t="n">
+        <f aca="false">COUNTIF(AB3:AB23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AC25" s="1" t="n">
+        <f aca="false">COUNTIF(AC3:AC23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AD25" s="1" t="n">
+        <f aca="false">COUNTIF(AD3:AD23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AE25" s="1" t="n">
+        <f aca="false">COUNTIF(AE3:AE23,"M")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="1" t="s">
@@ -4880,6 +5237,26 @@
         <f aca="false">COUNTIF(Z3:Z23,"T")</f>
         <v>0</v>
       </c>
+      <c r="AA26" s="1" t="n">
+        <f aca="false">COUNTIF(AA3:AA23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AB26" s="1" t="n">
+        <f aca="false">COUNTIF(AB3:AB23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AC26" s="1" t="n">
+        <f aca="false">COUNTIF(AC3:AC23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AD26" s="1" t="n">
+        <f aca="false">COUNTIF(AD3:AD23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AE26" s="1" t="n">
+        <f aca="false">COUNTIF(AE3:AE23,"T")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="s">
@@ -4896,6 +5273,26 @@
       <c r="Z27" s="1" t="n">
         <f aca="false">SUM(Z24:Z26)</f>
         <v>2</v>
+      </c>
+      <c r="AA27" s="1" t="n">
+        <f aca="false">SUM(AA24:AA26)</f>
+        <v>14</v>
+      </c>
+      <c r="AB27" s="1" t="n">
+        <f aca="false">SUM(AB24:AB26)</f>
+        <v>15</v>
+      </c>
+      <c r="AC27" s="1" t="n">
+        <f aca="false">SUM(AC24:AC26)</f>
+        <v>16</v>
+      </c>
+      <c r="AD27" s="1" t="n">
+        <f aca="false">SUM(AD24:AD26)</f>
+        <v>14</v>
+      </c>
+      <c r="AE27" s="1" t="n">
+        <f aca="false">SUM(AE24:AE26)</f>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -4942,13 +5339,15 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.34"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="35.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="1" width="8.68"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="6" min="6" style="1" width="11.78"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="9" min="7" style="1" width="8.75"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="10" style="1" width="10.37"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="11" min="11" style="1" width="8.75"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="13" min="13" style="1" width="8.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16145" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.78"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="7" style="1" width="8.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="10.37"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="8.75"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="14" min="14" style="1" width="8.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="13.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="13.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16151" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4976,32 +5375,41 @@
       <c r="F2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>49</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5009,13 +5417,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>8</v>
@@ -5023,37 +5431,46 @@
       <c r="F3" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="5"/>
+      <c r="H3" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="5"/>
+      <c r="J3" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="K3" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="L3" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="L3" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(E3,F3,G3,I3,J3,K3),0)</f>
+      <c r="M3" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(E3,F3,H3,J3,K3,L3),0)</f>
         <v>7</v>
       </c>
-      <c r="M3" s="5" t="str">
-        <f aca="false">IF(L3&gt;6,"TEA",IF(L3&gt;3,"TEP","TED"))</f>
+      <c r="N3" s="5" t="str">
+        <f aca="false">IF(M3&gt;6,"TEA",IF(M3&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N3" s="1" t="n">
+      <c r="O3" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O3" s="1" t="n">
-        <f aca="false">IF(AND(L3&gt;6,N3&gt;6),ROUND((L3+N3)/2,0),MIN(L3,N3))</f>
+      <c r="P3" s="1" t="n">
+        <f aca="false">IF(AND(M3&gt;6,O3&gt;6),ROUND((M3+O3)/2,0),MIN(M3,O3))</f>
         <v>8</v>
       </c>
-      <c r="P3" s="5" t="str">
-        <f aca="false">IF(O3&gt;6,"TEA",IF(O3&gt;3,"TEP","TED"))</f>
+      <c r="Q3" s="5" t="str">
+        <f aca="false">IF(P3&gt;6,"TEA",IF(P3&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5061,13 +5478,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>10</v>
@@ -5075,37 +5492,46 @@
       <c r="F4" s="5" t="n">
         <v>5.5</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="5"/>
+      <c r="H4" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5" t="n">
+      <c r="I4" s="5"/>
+      <c r="J4" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="K4" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="K4" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="L4" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(E4,F4,G4,I4,J4,K4),0)</f>
+        <v>10</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(E4,F4,H4,J4,K4,L4),0)</f>
         <v>8</v>
       </c>
-      <c r="M4" s="5" t="str">
-        <f aca="false">IF(L4&gt;6,"TEA",IF(L4&gt;3,"TEP","TED"))</f>
+      <c r="N4" s="5" t="str">
+        <f aca="false">IF(M4&gt;6,"TEA",IF(M4&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N4" s="1" t="n">
+      <c r="O4" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O4" s="1" t="n">
-        <f aca="false">IF(AND(L4&gt;6,N4&gt;6),ROUND((L4+N4)/2,0),MIN(L4,N4))</f>
+      <c r="P4" s="1" t="n">
+        <f aca="false">IF(AND(M4&gt;6,O4&gt;6),ROUND((M4+O4)/2,0),MIN(M4,O4))</f>
         <v>8</v>
       </c>
-      <c r="P4" s="5" t="str">
-        <f aca="false">IF(O4&gt;6,"TEA",IF(O4&gt;3,"TEP","TED"))</f>
+      <c r="Q4" s="5" t="str">
+        <f aca="false">IF(P4&gt;6,"TEA",IF(P4&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5113,13 +5539,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>1</v>
@@ -5127,37 +5553,46 @@
       <c r="F5" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="5"/>
+      <c r="H5" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5" t="n">
-        <v>7</v>
-      </c>
+      <c r="I5" s="5"/>
       <c r="J5" s="5" t="n">
         <v>7</v>
       </c>
       <c r="K5" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="L5" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(E5,F5,G5,I5,J5,K5),0)</f>
+      <c r="M5" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(E5,F5,H5,J5,K5,L5),0)</f>
         <v>6</v>
       </c>
-      <c r="M5" s="5" t="str">
-        <f aca="false">IF(L5&gt;6,"TEA",IF(L5&gt;3,"TEP","TED"))</f>
+      <c r="N5" s="5" t="str">
+        <f aca="false">IF(M5&gt;6,"TEA",IF(M5&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="O5" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O5" s="1" t="n">
-        <f aca="false">IF(AND(L5&gt;6,N5&gt;6),ROUND((L5+N5)/2,0),MIN(L5,N5))</f>
+      <c r="P5" s="1" t="n">
+        <f aca="false">IF(AND(M5&gt;6,O5&gt;6),ROUND((M5+O5)/2,0),MIN(M5,O5))</f>
         <v>6</v>
       </c>
-      <c r="P5" s="5" t="str">
-        <f aca="false">IF(O5&gt;6,"TEA",IF(O5&gt;3,"TEP","TED"))</f>
+      <c r="Q5" s="5" t="str">
+        <f aca="false">IF(P5&gt;6,"TEA",IF(P5&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
+      </c>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5165,13 +5600,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>10</v>
@@ -5179,37 +5614,46 @@
       <c r="F6" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="G6" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5" t="n">
-        <v>10</v>
-      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" s="5"/>
       <c r="J6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="L6" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(E6,F6,G6,I6,J6,K6),0)</f>
-        <v>10</v>
-      </c>
-      <c r="M6" s="5" t="str">
-        <f aca="false">IF(L6&gt;6,"TEA",IF(L6&gt;3,"TEP","TED"))</f>
+        <v>10</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(E6,F6,H6,J6,K6,L6),0)</f>
+        <v>10</v>
+      </c>
+      <c r="N6" s="5" t="str">
+        <f aca="false">IF(M6&gt;6,"TEA",IF(M6&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="O6" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O6" s="1" t="n">
-        <f aca="false">IF(AND(L6&gt;6,N6&gt;6),ROUND((L6+N6)/2,0),MIN(L6,N6))</f>
+      <c r="P6" s="1" t="n">
+        <f aca="false">IF(AND(M6&gt;6,O6&gt;6),ROUND((M6+O6)/2,0),MIN(M6,O6))</f>
         <v>9</v>
       </c>
-      <c r="P6" s="5" t="str">
-        <f aca="false">IF(O6&gt;6,"TEA",IF(O6&gt;3,"TEP","TED"))</f>
+      <c r="Q6" s="5" t="str">
+        <f aca="false">IF(P6&gt;6,"TEA",IF(P6&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5217,13 +5661,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>8</v>
@@ -5231,39 +5675,48 @@
       <c r="F7" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="5"/>
+      <c r="H7" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="I7" s="3" t="n">
         <v>46135</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="J7" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="J7" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="K7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="L7" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(E7,F7,G7,I7,J7,K7),0)</f>
+      <c r="M7" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(E7,F7,H7,J7,K7,L7),0)</f>
         <v>9</v>
       </c>
-      <c r="M7" s="5" t="str">
-        <f aca="false">IF(L7&gt;6,"TEA",IF(L7&gt;3,"TEP","TED"))</f>
+      <c r="N7" s="5" t="str">
+        <f aca="false">IF(M7&gt;6,"TEA",IF(M7&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N7" s="1" t="n">
+      <c r="O7" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O7" s="1" t="n">
-        <f aca="false">IF(AND(L7&gt;6,N7&gt;6),ROUND((L7+N7)/2,0),MIN(L7,N7))</f>
+      <c r="P7" s="1" t="n">
+        <f aca="false">IF(AND(M7&gt;6,O7&gt;6),ROUND((M7+O7)/2,0),MIN(M7,O7))</f>
         <v>9</v>
       </c>
-      <c r="P7" s="5" t="str">
-        <f aca="false">IF(O7&gt;6,"TEA",IF(O7&gt;3,"TEP","TED"))</f>
+      <c r="Q7" s="5" t="str">
+        <f aca="false">IF(P7&gt;6,"TEA",IF(P7&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5271,13 +5724,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>8</v>
@@ -5285,45 +5738,47 @@
       <c r="F8" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="G8" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5" t="n">
+      <c r="G8" s="5"/>
+      <c r="H8" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="J8" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="K8" s="5" t="n">
         <v>10</v>
       </c>
       <c r="L8" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(E8,F8,G8,I8,J8,K8),0)</f>
-        <v>10</v>
-      </c>
-      <c r="M8" s="5" t="str">
-        <f aca="false">IF(L8&gt;6,"TEA",IF(L8&gt;3,"TEP","TED"))</f>
+        <v>10</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(E8,F8,H8,J8,K8,L8),0)</f>
+        <v>10</v>
+      </c>
+      <c r="N8" s="5" t="str">
+        <f aca="false">IF(M8&gt;6,"TEA",IF(M8&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N8" s="1" t="n">
+      <c r="O8" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O8" s="1" t="n">
-        <f aca="false">IF(AND(L8&gt;6,N8&gt;6),ROUND((L8+N8)/2,0),MIN(L8,N8))</f>
+      <c r="P8" s="1" t="n">
+        <f aca="false">IF(AND(M8&gt;6,O8&gt;6),ROUND((M8+O8)/2,0),MIN(M8,O8))</f>
         <v>9</v>
       </c>
-      <c r="P8" s="5" t="str">
-        <f aca="false">IF(O8&gt;6,"TEA",IF(O8&gt;3,"TEP","TED"))</f>
+      <c r="Q8" s="5" t="str">
+        <f aca="false">IF(P8&gt;6,"TEA",IF(P8&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
@@ -5411,12 +5866,12 @@
       <c r="DD8" s="1"/>
       <c r="DE8" s="1"/>
       <c r="DF8" s="1"/>
-      <c r="WVY8" s="1"/>
-      <c r="WVZ8" s="1"/>
-      <c r="WWA8" s="1"/>
-      <c r="WWB8" s="1"/>
-      <c r="WWC8" s="1"/>
-      <c r="WWD8" s="1"/>
+      <c r="DG8" s="1"/>
+      <c r="DH8" s="1"/>
+      <c r="DI8" s="1"/>
+      <c r="DJ8" s="1"/>
+      <c r="DK8" s="1"/>
+      <c r="DL8" s="1"/>
       <c r="WWE8" s="1"/>
       <c r="WWF8" s="1"/>
       <c r="WWG8" s="1"/>
@@ -5465,19 +5920,25 @@
       <c r="WXX8" s="1"/>
       <c r="WXY8" s="1"/>
       <c r="WXZ8" s="1"/>
+      <c r="WYA8" s="1"/>
+      <c r="WYB8" s="1"/>
+      <c r="WYC8" s="1"/>
+      <c r="WYD8" s="1"/>
+      <c r="WYE8" s="1"/>
+      <c r="WYF8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>8</v>
@@ -5485,37 +5946,46 @@
       <c r="F9" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="5"/>
+      <c r="H9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="I9" s="5"/>
       <c r="J9" s="5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K9" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="L9" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(E9,F9,G9,I9,J9,K9),0)</f>
+      <c r="M9" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(E9,F9,H9,J9,K9,L9),0)</f>
         <v>8</v>
       </c>
-      <c r="M9" s="5" t="str">
-        <f aca="false">IF(L9&gt;6,"TEA",IF(L9&gt;3,"TEP","TED"))</f>
+      <c r="N9" s="5" t="str">
+        <f aca="false">IF(M9&gt;6,"TEA",IF(M9&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N9" s="1" t="n">
+      <c r="O9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O9" s="1" t="n">
-        <f aca="false">IF(AND(L9&gt;6,N9&gt;6),ROUND((L9+N9)/2,0),MIN(L9,N9))</f>
+      <c r="P9" s="1" t="n">
+        <f aca="false">IF(AND(M9&gt;6,O9&gt;6),ROUND((M9+O9)/2,0),MIN(M9,O9))</f>
         <v>8</v>
       </c>
-      <c r="P9" s="5" t="str">
-        <f aca="false">IF(O9&gt;6,"TEA",IF(O9&gt;3,"TEP","TED"))</f>
+      <c r="Q9" s="5" t="str">
+        <f aca="false">IF(P9&gt;6,"TEA",IF(P9&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5523,13 +5993,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>10</v>
@@ -5537,13 +6007,11 @@
       <c r="F10" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="G10" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5" t="n">
-        <v>10</v>
-      </c>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" s="5"/>
       <c r="J10" s="5" t="n">
         <v>10</v>
       </c>
@@ -5551,23 +6019,34 @@
         <v>10</v>
       </c>
       <c r="L10" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(E10,F10,G10,I10,J10,K10),0)</f>
-        <v>10</v>
-      </c>
-      <c r="M10" s="5" t="str">
-        <f aca="false">IF(L10&gt;6,"TEA",IF(L10&gt;3,"TEP","TED"))</f>
+        <v>10</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(E10,F10,H10,J10,K10,L10),0)</f>
+        <v>10</v>
+      </c>
+      <c r="N10" s="5" t="str">
+        <f aca="false">IF(M10&gt;6,"TEA",IF(M10&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N10" s="1" t="n">
+      <c r="O10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O10" s="1" t="n">
-        <f aca="false">IF(AND(L10&gt;6,N10&gt;6),ROUND((L10+N10)/2,0),MIN(L10,N10))</f>
+      <c r="P10" s="1" t="n">
+        <f aca="false">IF(AND(M10&gt;6,O10&gt;6),ROUND((M10+O10)/2,0),MIN(M10,O10))</f>
         <v>9</v>
       </c>
-      <c r="P10" s="5" t="str">
-        <f aca="false">IF(O10&gt;6,"TEA",IF(O10&gt;3,"TEP","TED"))</f>
+      <c r="Q10" s="5" t="str">
+        <f aca="false">IF(P10&gt;6,"TEA",IF(P10&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5575,13 +6054,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>10</v>
@@ -5589,37 +6068,46 @@
       <c r="F11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="G11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5" t="n">
+      <c r="G11" s="5"/>
+      <c r="H11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="J11" s="5" t="n">
+      <c r="K11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="K11" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="L11" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(E11,F11,G11,I11,J11,K11),0)</f>
+        <v>10</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(E11,F11,H11,J11,K11,L11),0)</f>
         <v>9</v>
       </c>
-      <c r="M11" s="5" t="str">
-        <f aca="false">IF(L11&gt;6,"TEA",IF(L11&gt;3,"TEP","TED"))</f>
+      <c r="N11" s="5" t="str">
+        <f aca="false">IF(M11&gt;6,"TEA",IF(M11&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N11" s="1" t="n">
+      <c r="O11" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O11" s="1" t="n">
-        <f aca="false">IF(AND(L11&gt;6,N11&gt;6),ROUND((L11+N11)/2,0),MIN(L11,N11))</f>
+      <c r="P11" s="1" t="n">
+        <f aca="false">IF(AND(M11&gt;6,O11&gt;6),ROUND((M11+O11)/2,0),MIN(M11,O11))</f>
         <v>9</v>
       </c>
-      <c r="P11" s="5" t="str">
-        <f aca="false">IF(O11&gt;6,"TEA",IF(O11&gt;3,"TEP","TED"))</f>
+      <c r="Q11" s="5" t="str">
+        <f aca="false">IF(P11&gt;6,"TEA",IF(P11&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="12" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5627,13 +6115,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
@@ -5641,45 +6129,47 @@
       <c r="F12" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(E12,F12,G12,I12,J12,K12),0)</f>
-        <v>1</v>
-      </c>
-      <c r="M12" s="5" t="str">
-        <f aca="false">IF(L12&gt;6,"TEA",IF(L12&gt;3,"TEP","TED"))</f>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(E12,F12,H12,J12,K12,L12),0)</f>
+        <v>1</v>
+      </c>
+      <c r="N12" s="5" t="str">
+        <f aca="false">IF(M12&gt;6,"TEA",IF(M12&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="N12" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="O12" s="1" t="n">
-        <f aca="false">IF(AND(L12&gt;6,N12&gt;6),ROUND((L12+N12)/2,0),MIN(L12,N12))</f>
-        <v>1</v>
-      </c>
-      <c r="P12" s="5" t="str">
-        <f aca="false">IF(O12&gt;6,"TEA",IF(O12&gt;3,"TEP","TED"))</f>
+        <v>1</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <f aca="false">IF(AND(M12&gt;6,O12&gt;6),ROUND((M12+O12)/2,0),MIN(M12,O12))</f>
+        <v>1</v>
+      </c>
+      <c r="Q12" s="5" t="str">
+        <f aca="false">IF(P12&gt;6,"TEA",IF(P12&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
-      <c r="T12" s="6"/>
-      <c r="U12" s="6"/>
-      <c r="V12" s="6"/>
-      <c r="W12" s="6"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+      <c r="W12" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="X12" s="6"/>
       <c r="Y12" s="6"/>
       <c r="Z12" s="6"/>
@@ -5767,12 +6257,12 @@
       <c r="DD12" s="6"/>
       <c r="DE12" s="6"/>
       <c r="DF12" s="6"/>
-      <c r="WVY12" s="6"/>
-      <c r="WVZ12" s="6"/>
-      <c r="WWA12" s="6"/>
-      <c r="WWB12" s="6"/>
-      <c r="WWC12" s="6"/>
-      <c r="WWD12" s="6"/>
+      <c r="DG12" s="6"/>
+      <c r="DH12" s="6"/>
+      <c r="DI12" s="6"/>
+      <c r="DJ12" s="6"/>
+      <c r="DK12" s="6"/>
+      <c r="DL12" s="6"/>
       <c r="WWE12" s="6"/>
       <c r="WWF12" s="6"/>
       <c r="WWG12" s="6"/>
@@ -5821,19 +6311,25 @@
       <c r="WXX12" s="6"/>
       <c r="WXY12" s="6"/>
       <c r="WXZ12" s="6"/>
+      <c r="WYA12" s="6"/>
+      <c r="WYB12" s="6"/>
+      <c r="WYC12" s="6"/>
+      <c r="WYD12" s="6"/>
+      <c r="WYE12" s="6"/>
+      <c r="WYF12" s="6"/>
     </row>
     <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>10</v>
@@ -5841,37 +6337,46 @@
       <c r="F13" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="G13" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5" t="n">
+      <c r="G13" s="5"/>
+      <c r="H13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="J13" s="5" t="n">
+      <c r="K13" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="L13" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(E13,F13,G13,I13,J13,K13),0)</f>
+        <v>10</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(E13,F13,H13,J13,K13,L13),0)</f>
         <v>9</v>
       </c>
-      <c r="M13" s="5" t="str">
-        <f aca="false">IF(L13&gt;6,"TEA",IF(L13&gt;3,"TEP","TED"))</f>
+      <c r="N13" s="5" t="str">
+        <f aca="false">IF(M13&gt;6,"TEA",IF(M13&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N13" s="1" t="n">
+      <c r="O13" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O13" s="1" t="n">
-        <f aca="false">IF(AND(L13&gt;6,N13&gt;6),ROUND((L13+N13)/2,0),MIN(L13,N13))</f>
+      <c r="P13" s="1" t="n">
+        <f aca="false">IF(AND(M13&gt;6,O13&gt;6),ROUND((M13+O13)/2,0),MIN(M13,O13))</f>
         <v>9</v>
       </c>
-      <c r="P13" s="5" t="str">
-        <f aca="false">IF(O13&gt;6,"TEA",IF(O13&gt;3,"TEP","TED"))</f>
+      <c r="Q13" s="5" t="str">
+        <f aca="false">IF(P13&gt;6,"TEA",IF(P13&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5879,13 +6384,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>10</v>
@@ -5893,37 +6398,46 @@
       <c r="F14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="5"/>
+      <c r="H14" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5" t="n">
+      <c r="I14" s="5"/>
+      <c r="J14" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="J14" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="K14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="L14" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(E14,F14,G14,I14,J14,K14),0)</f>
-        <v>10</v>
-      </c>
-      <c r="M14" s="5" t="str">
-        <f aca="false">IF(L14&gt;6,"TEA",IF(L14&gt;3,"TEP","TED"))</f>
+      <c r="M14" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(E14,F14,H14,J14,K14,L14),0)</f>
+        <v>10</v>
+      </c>
+      <c r="N14" s="5" t="str">
+        <f aca="false">IF(M14&gt;6,"TEA",IF(M14&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N14" s="1" t="n">
+      <c r="O14" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O14" s="1" t="n">
-        <f aca="false">IF(AND(L14&gt;6,N14&gt;6),ROUND((L14+N14)/2,0),MIN(L14,N14))</f>
+      <c r="P14" s="1" t="n">
+        <f aca="false">IF(AND(M14&gt;6,O14&gt;6),ROUND((M14+O14)/2,0),MIN(M14,O14))</f>
         <v>9</v>
       </c>
-      <c r="P14" s="5" t="str">
-        <f aca="false">IF(O14&gt;6,"TEA",IF(O14&gt;3,"TEP","TED"))</f>
+      <c r="Q14" s="5" t="str">
+        <f aca="false">IF(P14&gt;6,"TEA",IF(P14&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="15" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5931,13 +6445,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>1</v>
@@ -5945,45 +6459,47 @@
       <c r="F15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(E15,F15,G15,I15,J15,K15),0)</f>
-        <v>1</v>
-      </c>
-      <c r="M15" s="5" t="str">
-        <f aca="false">IF(L15&gt;6,"TEA",IF(L15&gt;3,"TEP","TED"))</f>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(E15,F15,H15,J15,K15,L15),0)</f>
+        <v>1</v>
+      </c>
+      <c r="N15" s="5" t="str">
+        <f aca="false">IF(M15&gt;6,"TEA",IF(M15&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="N15" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="O15" s="1" t="n">
-        <f aca="false">IF(AND(L15&gt;6,N15&gt;6),ROUND((L15+N15)/2,0),MIN(L15,N15))</f>
-        <v>1</v>
-      </c>
-      <c r="P15" s="5" t="str">
-        <f aca="false">IF(O15&gt;6,"TEA",IF(O15&gt;3,"TEP","TED"))</f>
+        <v>1</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <f aca="false">IF(AND(M15&gt;6,O15&gt;6),ROUND((M15+O15)/2,0),MIN(M15,O15))</f>
+        <v>1</v>
+      </c>
+      <c r="Q15" s="5" t="str">
+        <f aca="false">IF(P15&gt;6,"TEA",IF(P15&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="6"/>
-      <c r="S15" s="6"/>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
-      <c r="V15" s="6"/>
-      <c r="W15" s="6"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="X15" s="6"/>
       <c r="Y15" s="6"/>
       <c r="Z15" s="6"/>
@@ -6071,12 +6587,12 @@
       <c r="DD15" s="6"/>
       <c r="DE15" s="6"/>
       <c r="DF15" s="6"/>
-      <c r="WVY15" s="6"/>
-      <c r="WVZ15" s="6"/>
-      <c r="WWA15" s="6"/>
-      <c r="WWB15" s="6"/>
-      <c r="WWC15" s="6"/>
-      <c r="WWD15" s="6"/>
+      <c r="DG15" s="6"/>
+      <c r="DH15" s="6"/>
+      <c r="DI15" s="6"/>
+      <c r="DJ15" s="6"/>
+      <c r="DK15" s="6"/>
+      <c r="DL15" s="6"/>
       <c r="WWE15" s="6"/>
       <c r="WWF15" s="6"/>
       <c r="WWG15" s="6"/>
@@ -6125,19 +6641,25 @@
       <c r="WXX15" s="6"/>
       <c r="WXY15" s="6"/>
       <c r="WXZ15" s="6"/>
+      <c r="WYA15" s="6"/>
+      <c r="WYB15" s="6"/>
+      <c r="WYC15" s="6"/>
+      <c r="WYD15" s="6"/>
+      <c r="WYE15" s="6"/>
+      <c r="WYF15" s="6"/>
     </row>
     <row r="16" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>8</v>
@@ -6145,37 +6667,46 @@
       <c r="F16" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5" t="n">
-        <v>10</v>
-      </c>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" s="5"/>
       <c r="J16" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K16" s="5" t="n">
         <v>6.9</v>
       </c>
-      <c r="K16" s="5" t="n">
+      <c r="L16" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="L16" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(E16,F16,G16,I16,J16,K16),0)</f>
+      <c r="M16" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(E16,F16,H16,J16,K16,L16),0)</f>
         <v>9</v>
       </c>
-      <c r="M16" s="5" t="str">
-        <f aca="false">IF(L16&gt;6,"TEA",IF(L16&gt;3,"TEP","TED"))</f>
+      <c r="N16" s="5" t="str">
+        <f aca="false">IF(M16&gt;6,"TEA",IF(M16&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N16" s="1" t="n">
+      <c r="O16" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O16" s="1" t="n">
-        <f aca="false">IF(AND(L16&gt;6,N16&gt;6),ROUND((L16+N16)/2,0),MIN(L16,N16))</f>
+      <c r="P16" s="1" t="n">
+        <f aca="false">IF(AND(M16&gt;6,O16&gt;6),ROUND((M16+O16)/2,0),MIN(M16,O16))</f>
         <v>9</v>
       </c>
-      <c r="P16" s="5" t="str">
-        <f aca="false">IF(O16&gt;6,"TEA",IF(O16&gt;3,"TEP","TED"))</f>
+      <c r="Q16" s="5" t="str">
+        <f aca="false">IF(P16&gt;6,"TEA",IF(P16&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="W16" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6183,13 +6714,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>10</v>
@@ -6197,37 +6728,48 @@
       <c r="F17" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="G17" s="5"/>
+      <c r="H17" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5" t="n">
+      <c r="I17" s="5"/>
+      <c r="J17" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="J17" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="K17" s="5" t="n">
         <v>10</v>
       </c>
       <c r="L17" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(E17,F17,G17,I17,J17,K17),0)</f>
+        <v>10</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(E17,F17,H17,J17,K17,L17),0)</f>
         <v>8</v>
       </c>
-      <c r="M17" s="5" t="str">
-        <f aca="false">IF(L17&gt;6,"TEA",IF(L17&gt;3,"TEP","TED"))</f>
+      <c r="N17" s="5" t="str">
+        <f aca="false">IF(M17&gt;6,"TEA",IF(M17&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N17" s="1" t="n">
+      <c r="O17" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O17" s="1" t="n">
-        <f aca="false">IF(AND(L17&gt;6,N17&gt;6),ROUND((L17+N17)/2,0),MIN(L17,N17))</f>
+      <c r="P17" s="1" t="n">
+        <f aca="false">IF(AND(M17&gt;6,O17&gt;6),ROUND((M17+O17)/2,0),MIN(M17,O17))</f>
         <v>8</v>
       </c>
-      <c r="P17" s="5" t="str">
-        <f aca="false">IF(O17&gt;6,"TEA",IF(O17&gt;3,"TEP","TED"))</f>
+      <c r="Q17" s="5" t="str">
+        <f aca="false">IF(P17&gt;6,"TEA",IF(P17&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R17" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+      <c r="W17" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="18" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6235,13 +6777,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>1</v>
@@ -6249,45 +6791,47 @@
       <c r="F18" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(E18,F18,G18,I18,J18,K18),0)</f>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(E18,F18,H18,J18,K18,L18),0)</f>
         <v>3</v>
       </c>
-      <c r="M18" s="5" t="str">
-        <f aca="false">IF(L18&gt;6,"TEA",IF(L18&gt;3,"TEP","TED"))</f>
+      <c r="N18" s="5" t="str">
+        <f aca="false">IF(M18&gt;6,"TEA",IF(M18&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="N18" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="O18" s="1" t="n">
-        <f aca="false">IF(AND(L18&gt;6,N18&gt;6),ROUND((L18+N18)/2,0),MIN(L18,N18))</f>
-        <v>1</v>
-      </c>
-      <c r="P18" s="5" t="str">
-        <f aca="false">IF(O18&gt;6,"TEA",IF(O18&gt;3,"TEP","TED"))</f>
+        <v>1</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <f aca="false">IF(AND(M18&gt;6,O18&gt;6),ROUND((M18+O18)/2,0),MIN(M18,O18))</f>
+        <v>1</v>
+      </c>
+      <c r="Q18" s="5" t="str">
+        <f aca="false">IF(P18&gt;6,"TEA",IF(P18&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="6"/>
-      <c r="V18" s="6"/>
-      <c r="W18" s="6"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="X18" s="6"/>
       <c r="Y18" s="6"/>
       <c r="Z18" s="6"/>
@@ -6375,12 +6919,12 @@
       <c r="DD18" s="6"/>
       <c r="DE18" s="6"/>
       <c r="DF18" s="6"/>
-      <c r="WVY18" s="6"/>
-      <c r="WVZ18" s="6"/>
-      <c r="WWA18" s="6"/>
-      <c r="WWB18" s="6"/>
-      <c r="WWC18" s="6"/>
-      <c r="WWD18" s="6"/>
+      <c r="DG18" s="6"/>
+      <c r="DH18" s="6"/>
+      <c r="DI18" s="6"/>
+      <c r="DJ18" s="6"/>
+      <c r="DK18" s="6"/>
+      <c r="DL18" s="6"/>
       <c r="WWE18" s="6"/>
       <c r="WWF18" s="6"/>
       <c r="WWG18" s="6"/>
@@ -6429,19 +6973,25 @@
       <c r="WXX18" s="6"/>
       <c r="WXY18" s="6"/>
       <c r="WXZ18" s="6"/>
+      <c r="WYA18" s="6"/>
+      <c r="WYB18" s="6"/>
+      <c r="WYC18" s="6"/>
+      <c r="WYD18" s="6"/>
+      <c r="WYE18" s="6"/>
+      <c r="WYF18" s="6"/>
     </row>
     <row r="19" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="n">
         <v>17</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>1</v>
@@ -6449,45 +6999,47 @@
       <c r="F19" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(E19,F19,G19,I19,J19,K19),0)</f>
-        <v>1</v>
-      </c>
-      <c r="M19" s="5" t="str">
-        <f aca="false">IF(L19&gt;6,"TEA",IF(L19&gt;3,"TEP","TED"))</f>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(E19,F19,H19,J19,K19,L19),0)</f>
+        <v>1</v>
+      </c>
+      <c r="N19" s="5" t="str">
+        <f aca="false">IF(M19&gt;6,"TEA",IF(M19&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="N19" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="O19" s="1" t="n">
-        <f aca="false">IF(AND(L19&gt;6,N19&gt;6),ROUND((L19+N19)/2,0),MIN(L19,N19))</f>
-        <v>1</v>
-      </c>
-      <c r="P19" s="5" t="str">
-        <f aca="false">IF(O19&gt;6,"TEA",IF(O19&gt;3,"TEP","TED"))</f>
+        <v>1</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <f aca="false">IF(AND(M19&gt;6,O19&gt;6),ROUND((M19+O19)/2,0),MIN(M19,O19))</f>
+        <v>1</v>
+      </c>
+      <c r="Q19" s="5" t="str">
+        <f aca="false">IF(P19&gt;6,"TEA",IF(P19&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="Q19" s="6"/>
-      <c r="R19" s="6"/>
-      <c r="S19" s="6"/>
-      <c r="T19" s="6"/>
-      <c r="U19" s="6"/>
-      <c r="V19" s="6"/>
-      <c r="W19" s="6"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="X19" s="6"/>
       <c r="Y19" s="6"/>
       <c r="Z19" s="6"/>
@@ -6575,12 +7127,12 @@
       <c r="DD19" s="6"/>
       <c r="DE19" s="6"/>
       <c r="DF19" s="6"/>
-      <c r="WVY19" s="6"/>
-      <c r="WVZ19" s="6"/>
-      <c r="WWA19" s="6"/>
-      <c r="WWB19" s="6"/>
-      <c r="WWC19" s="6"/>
-      <c r="WWD19" s="6"/>
+      <c r="DG19" s="6"/>
+      <c r="DH19" s="6"/>
+      <c r="DI19" s="6"/>
+      <c r="DJ19" s="6"/>
+      <c r="DK19" s="6"/>
+      <c r="DL19" s="6"/>
       <c r="WWE19" s="6"/>
       <c r="WWF19" s="6"/>
       <c r="WWG19" s="6"/>
@@ -6629,57 +7181,74 @@
       <c r="WXX19" s="6"/>
       <c r="WXY19" s="6"/>
       <c r="WXZ19" s="6"/>
+      <c r="WYA19" s="6"/>
+      <c r="WYB19" s="6"/>
+      <c r="WYC19" s="6"/>
+      <c r="WYD19" s="6"/>
+      <c r="WYE19" s="6"/>
+      <c r="WYF19" s="6"/>
     </row>
     <row r="20" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>10</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>46170</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" s="5"/>
       <c r="J20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="K20" s="5" t="n">
+      <c r="L20" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="L20" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(E20,F20,G20,I20,J20,K20),0)</f>
-        <v>5</v>
-      </c>
-      <c r="M20" s="5" t="str">
-        <f aca="false">IF(L20&gt;6,"TEA",IF(L20&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
-      </c>
-      <c r="N20" s="1" t="n">
+      <c r="M20" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(E20,F20,H20,J20,K20,L20),0)</f>
+        <v>7</v>
+      </c>
+      <c r="N20" s="5" t="str">
+        <f aca="false">IF(M20&gt;6,"TEA",IF(M20&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O20" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O20" s="1" t="n">
-        <f aca="false">IF(AND(L20&gt;6,N20&gt;6),ROUND((L20+N20)/2,0),MIN(L20,N20))</f>
-        <v>5</v>
-      </c>
-      <c r="P20" s="5" t="str">
-        <f aca="false">IF(O20&gt;6,"TEA",IF(O20&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+      <c r="P20" s="1" t="n">
+        <f aca="false">IF(AND(M20&gt;6,O20&gt;6),ROUND((M20+O20)/2,0),MIN(M20,O20))</f>
+        <v>8</v>
+      </c>
+      <c r="Q20" s="5" t="str">
+        <f aca="false">IF(P20&gt;6,"TEA",IF(P20&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6687,13 +7256,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>7</v>
@@ -6701,37 +7270,46 @@
       <c r="F21" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="G21" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5" t="n">
+      <c r="G21" s="5"/>
+      <c r="H21" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <v>8</v>
       </c>
       <c r="K21" s="5" t="n">
         <v>8</v>
       </c>
       <c r="L21" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(E21,F21,G21,I21,J21,K21),0)</f>
         <v>8</v>
       </c>
-      <c r="M21" s="5" t="str">
-        <f aca="false">IF(L21&gt;6,"TEA",IF(L21&gt;3,"TEP","TED"))</f>
+      <c r="M21" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(E21,F21,H21,J21,K21,L21),0)</f>
+        <v>8</v>
+      </c>
+      <c r="N21" s="5" t="str">
+        <f aca="false">IF(M21&gt;6,"TEA",IF(M21&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N21" s="1" t="n">
+      <c r="O21" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O21" s="1" t="n">
-        <f aca="false">IF(AND(L21&gt;6,N21&gt;6),ROUND((L21+N21)/2,0),MIN(L21,N21))</f>
+      <c r="P21" s="1" t="n">
+        <f aca="false">IF(AND(M21&gt;6,O21&gt;6),ROUND((M21+O21)/2,0),MIN(M21,O21))</f>
         <v>8</v>
       </c>
-      <c r="P21" s="5" t="str">
-        <f aca="false">IF(O21&gt;6,"TEA",IF(O21&gt;3,"TEP","TED"))</f>
+      <c r="Q21" s="5" t="str">
+        <f aca="false">IF(P21&gt;6,"TEA",IF(P21&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6739,13 +7317,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>10</v>
@@ -6753,44 +7331,47 @@
       <c r="F22" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="G22" s="5"/>
+      <c r="H22" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5" t="n">
-        <v>10</v>
-      </c>
+      <c r="I22" s="5"/>
       <c r="J22" s="5" t="n">
         <v>10</v>
       </c>
       <c r="K22" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L22" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="L22" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(E22,F22,G22,I22,J22,K22),0)</f>
-        <v>10</v>
-      </c>
-      <c r="M22" s="5" t="str">
-        <f aca="false">IF(L22&gt;6,"TEA",IF(L22&gt;3,"TEP","TED"))</f>
+      <c r="M22" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(E22,F22,H22,J22,K22,L22),0)</f>
+        <v>10</v>
+      </c>
+      <c r="N22" s="5" t="str">
+        <f aca="false">IF(M22&gt;6,"TEA",IF(M22&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="N22" s="1" t="n">
+      <c r="O22" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O22" s="1" t="n">
-        <f aca="false">IF(AND(L22&gt;6,N22&gt;6),ROUND((L22+N22)/2,0),MIN(L22,N22))</f>
+      <c r="P22" s="1" t="n">
+        <f aca="false">IF(AND(M22&gt;6,O22&gt;6),ROUND((M22+O22)/2,0),MIN(M22,O22))</f>
         <v>9</v>
       </c>
-      <c r="P22" s="5" t="str">
-        <f aca="false">IF(O22&gt;6,"TEA",IF(O22&gt;3,"TEP","TED"))</f>
+      <c r="Q22" s="5" t="str">
+        <f aca="false">IF(P22&gt;6,"TEA",IF(P22&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="WYA22" s="2"/>
-      <c r="WYB22" s="2"/>
-      <c r="WYC22" s="2"/>
-      <c r="WYD22" s="2"/>
-      <c r="WYE22" s="2"/>
-      <c r="WYF22" s="2"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="WYG22" s="2"/>
       <c r="WYH22" s="2"/>
       <c r="WYI22" s="2"/>
@@ -6977,13 +7558,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>36</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>1</v>
@@ -6991,45 +7572,47 @@
       <c r="F23" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="6"/>
       <c r="J23" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="L23" s="6" t="n">
-        <f aca="false">ROUND(AVERAGE(E23,F23,G23,I23,J23,K23),0)</f>
-        <v>1</v>
-      </c>
-      <c r="M23" s="6" t="str">
-        <f aca="false">IF(L23&gt;6,"TEA",IF(L23&gt;3,"TEP","TED"))</f>
+      <c r="M23" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(E23,F23,H23,J23,K23,L23),0)</f>
+        <v>1</v>
+      </c>
+      <c r="N23" s="6" t="str">
+        <f aca="false">IF(M23&gt;6,"TEA",IF(M23&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="N23" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="O23" s="1" t="n">
-        <f aca="false">IF(AND(L23&gt;6,N23&gt;6),ROUND((L23+N23)/2,0),MIN(L23,N23))</f>
-        <v>1</v>
-      </c>
-      <c r="P23" s="5" t="str">
-        <f aca="false">IF(O23&gt;6,"TEA",IF(O23&gt;3,"TEP","TED"))</f>
+        <v>1</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <f aca="false">IF(AND(M23&gt;6,O23&gt;6),ROUND((M23+O23)/2,0),MIN(M23,O23))</f>
+        <v>1</v>
+      </c>
+      <c r="Q23" s="5" t="str">
+        <f aca="false">IF(P23&gt;6,"TEA",IF(P23&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="Q23" s="6"/>
-      <c r="R23" s="6"/>
-      <c r="S23" s="6"/>
-      <c r="T23" s="6"/>
-      <c r="U23" s="6"/>
-      <c r="V23" s="6"/>
-      <c r="W23" s="6"/>
+      <c r="R23" s="5"/>
+      <c r="S23" s="5"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
+      <c r="V23" s="5"/>
+      <c r="W23" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="X23" s="6"/>
       <c r="Y23" s="6"/>
       <c r="Z23" s="6"/>
@@ -7117,12 +7700,12 @@
       <c r="DD23" s="6"/>
       <c r="DE23" s="6"/>
       <c r="DF23" s="6"/>
-      <c r="WVY23" s="6"/>
-      <c r="WVZ23" s="6"/>
-      <c r="WWA23" s="6"/>
-      <c r="WWB23" s="6"/>
-      <c r="WWC23" s="6"/>
-      <c r="WWD23" s="6"/>
+      <c r="DG23" s="6"/>
+      <c r="DH23" s="6"/>
+      <c r="DI23" s="6"/>
+      <c r="DJ23" s="6"/>
+      <c r="DK23" s="6"/>
+      <c r="DL23" s="6"/>
       <c r="WWE23" s="6"/>
       <c r="WWF23" s="6"/>
       <c r="WWG23" s="6"/>
@@ -7359,7 +7942,7 @@
       <c r="XFD23" s="6"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E3:M23 P3:P23">
+  <conditionalFormatting sqref="E3:N23 Q3:V23">
     <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
@@ -7383,7 +7966,7 @@
       <formula>"TED"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N3:O23">
+  <conditionalFormatting sqref="O3:P23">
     <cfRule type="cellIs" priority="9" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>6</formula>
     </cfRule>
@@ -7430,16 +8013,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7858,7 +8441,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F29" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G29" s="1" t="n">
         <f aca="false">COUNTIF(G2:G28,"&gt;0")</f>
@@ -7900,7 +8483,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8225,16 +8808,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8689,7 +9272,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
